--- a/docs/ASM67_55_Villains_11_Wizards_1_Final_Wizard_Tracker.xlsx
+++ b/docs/ASM67_55_Villains_11_Wizards_1_Final_Wizard_Tracker.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R006c123aa7a04eac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R38c31400023e4440"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R0363c6d162c94898"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="Rfdbfd60419bb4758"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Ra11a96024e514035"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Rfd7187014db84125"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R2b7c69b36ab748cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Rf105de0adef241a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Ra022d5db1baa4602"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R1246cfc7b78f4521"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Ra9fb2e4dc7a14ca5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R93ac9bb71bdb47e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="Rb755c8a637df4c30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rcc86d9586698491e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R14c5cfa286d746d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R96191e09dea14a75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R746b33da035f411a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Rfe98a6edb6964ff1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R3b8e4f9365d14b13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R1b6167c7f8ee4fce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R4d28c3fb74694c84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Red671b4d6beb47db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Rc8fbcba9b0304743"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R2bfb5926385f48aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R146aa5d17e674aa6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R5970563b55154c0e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2945,25 +2945,17 @@
           <x:t xml:space="preserve">Webs, drops, pops, VUK</x:t>
         </x:is>
       </x:c>
-      <x:c r="J36" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">100K/150K pellets + 1M Super</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K36" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">4s moving shot; five pellets; 20s VUK</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L36" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Super / timer / ball end</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M36" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Daily Bugle gate lockout and held-ball eight-band flood finale.</x:t>
-        </x:is>
+      <x:c r="J36" s="31" t="str">
+        <x:v>100K/150K first five pellets; More JP extras 200K/250K or 300K/350K with Bigger; 1M Super</x:v>
+      </x:c>
+      <x:c r="K36" s="31" t="str">
+        <x:v>4s moving shot; five pellets; 20s VUK</x:v>
+      </x:c>
+      <x:c r="L36" s="31" t="str">
+        <x:v>Super / timer / ball end</x:v>
+      </x:c>
+      <x:c r="M36" s="31" t="str">
+        <x:v>Orange E0E040 GI; active moving shot flashes green at 250ms on/off. Optional More JP pellets create risk/reward during the Super timer.</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -8940,10 +8932,8 @@
           <x:t xml:space="preserve">Implemented / needs playtest</x:t>
         </x:is>
       </x:c>
-      <x:c r="H36" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Oil Pellet Chase: red GI and one green shot sweep left web, left drops, left ...</x:t>
-        </x:is>
+      <x:c r="H36" s="31" t="str">
+        <x:v>Oil Pellet Chase: orange E0E040 GI and one flashing green shot sweep left web, left drops, left pop, center web, right pop, and right drops every 4 seconds. Collect five pellets to qualify the 1M reactor-flood VUK Super. More Jackpots leaves two optional higher-value pellets available during the Super.</x:v>
       </x:c>
       <x:c r="I36" s="31" t="inlineStr">
         <x:is>
@@ -12494,21 +12484,17 @@
           <x:t xml:space="preserve">1</x:t>
         </x:is>
       </x:c>
-      <x:c r="F36" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Follow one green moving shot across left web, left drops, left pop, center web, right pop, and right drops, reversing every 4 seconds.</x:t>
-        </x:is>
+      <x:c r="F36" s="31" t="str">
+        <x:v>Follow one flashing green moving shot across left web, left drops, left pop, center web, right pop, and right drops, reversing every 4 seconds. Collect five Oil Pellets.</x:v>
       </x:c>
       <x:c r="G36" s="31" t="str">
         <x:v>Five pellets open the gate and light the VUK for 20 seconds. A qualified VUK capture immediately cancels pending shared ejects/retries and arms the hold before the eight-band blue flood begins. The ball remains held through the four-second flood and villain summary; flood completion awards 1M.</x:v>
       </x:c>
-      <x:c r="H36" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Pellets 100K or 150K with Bigger. Wrong shots score only normal game points.</x:t>
-        </x:is>
+      <x:c r="H36" s="31" t="str">
+        <x:v>Pellets 1-5 score 100K, or 150K with Bigger. More Jackpots adds optional Pellet 6 at 200K and Pellet 7 at 250K; with Bigger too they are 300K and 350K. Wrong shots score only normal game points.</x:v>
       </x:c>
       <x:c r="I36" s="31" t="str">
-        <x:v>Implemented with moving-shot lighting, Super timer, eight-band flood, status and summary variables, Case Files, immediate qualified-VUK ownership through flood and summary, and the shared Master Vine route chase while the final VUK is lit. The chase clears on capture, timeout, or teardown. Needs machine playtest.</x:v>
+        <x:v>Implemented with 250ms green moving-shot flash, E0E040 orange GI, Super timer, eight-band flood, status/summary variables, Case Files, VUK hold through flood/summary, and the shared route chase. Needs machine playtest.</x:v>
       </x:c>
     </x:row>
     <x:row r="37">

--- a/docs/ASM67_55_Villains_11_Wizards_1_Final_Wizard_Tracker.xlsx
+++ b/docs/ASM67_55_Villains_11_Wizards_1_Final_Wizard_Tracker.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rcc86d9586698491e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R14c5cfa286d746d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R96191e09dea14a75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R746b33da035f411a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Rfe98a6edb6964ff1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R3b8e4f9365d14b13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R1b6167c7f8ee4fce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R4d28c3fb74694c84"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Red671b4d6beb47db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Rc8fbcba9b0304743"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R2bfb5926385f48aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R146aa5d17e674aa6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R5970563b55154c0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R5e89322b57934766"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R6f4760134a0a47b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R8e9588920f084747"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R43421266426f4323"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R078df61baac64514"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R6d868e37bab54ae3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Rf97cb9494d234408"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R04dde9cca1cb42da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R4416ec132511442d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R5a47c0d7efb34093"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Rcfe088a08840494a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="Rcfba3874cbbb4679"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R6ddcb59ede384b2e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2101,7 +2101,7 @@
         <x:v>Right-bank completion arms first post-reset drop to expand moving window 1 -&gt; 2 -&gt; 3; STAR freezes current window 10s/15s</x:v>
       </x:c>
       <x:c r="L21" s="31" t="str">
-        <x:v>One shipment, or two with More Jackpots / ball end</x:v>
+        <x:v>Three shipments, or four with More Jackpots / ball end</x:v>
       </x:c>
       <x:c r="M21" s="31" t="str">
         <x:v>Crime Wave risk/reward chase. Availability now grows through the approved one-, two-, and three-saucer moving windows. Only red hole lamps show valid saucers; scoring, chase speeds, Diamond Bonus, Case Files, red STAR flash, and terminal summary hold remain intact.</x:v>
@@ -2417,18 +2417,16 @@
         </x:is>
       </x:c>
       <x:c r="J27" s="31" t="str">
-        <x:v>Five chances; three correct required. More JP gives seven chances. Correct: 100K base, +50K each; Bigger JP: 150K base, +75K each. Wrong: 10K.</x:v>
+        <x:v>Four rounds; four correct required. More JP adds two recovery rounds. Clean JPs 200K/300K/400K/500K; first wrong -100K and removes that choice. Bigger: 300K/450K/600K/750K with -150K first-wrong penalty.</x:v>
       </x:c>
       <x:c r="K27" s="31" t="str">
-        <x:v>Lens-safe green indicators avoid weak red output through green bank inserts. Result GI restores after 350ms, and l_gi_a remains in the normal Pardo GI theme.</x:v>
+        <x:v>All live choices flash green identically. Reveal isolates the correct flashing choice. Summary tracks first-guess and second-guess Jackpots.</x:v>
       </x:c>
       <x:c r="L27" s="31" t="str">
-        <x:v>Third correct shot or final available chance</x:v>
-      </x:c>
-      <x:c r="M27" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Mystic chapter reveal/mistake-limit role.</x:t>
-        </x:is>
+        <x:v>Fourth correct Jackpot or final available recovery round</x:v>
+      </x:c>
+      <x:c r="M27" s="31" t="str">
+        <x:v>Mystic chapter reveal/mistake-limit role.</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -8538,7 +8536,7 @@
         </x:is>
       </x:c>
       <x:c r="G27" s="31" t="str">
-        <x:v>Implemented / recent spinner lighting fix</x:v>
+        <x:v>Four base rounds; More JP adds two recovery rounds. Each round presents three choices selected from seven logical shot groups; the three upper targets are one shared choice. All currently available choices flash green identically. Spinner reveals the correct choice for 4s, or 6s with More Time: the correct choice flashes and wrong choices go dark. First wrong scores 20K, removes that choice, and reduces the current Jackpot; the remaining two resume flashing. Second wrong loses the round. Four correct Jackpots defeat Pardo. Summary counts 1st-guess JPs and 2nd-guess JPs.</x:v>
       </x:c>
       <x:c r="H27" s="31" t="str">
         <x:v>Five chances, or seven with More JP. Each chance presents three choices selected from seven logical shot groups; the three upper targets are one shared upper-target group so they can never show conflicting good/bad states. Spinner reveals the correct choice for 4s, or 6s with More Time. Three correct shots defeats Pardo immediately. Using all chances with fewer than three correct shots produces the escape result. Hidden choices use solid green for white/green lens compatibility; reveal flashes only the correct green choice and turns wrong choices off. The main spinner insert flashes white while choices are hidden, turns off during the reveal, and resumes if another reveal is needed. Result GI flashes for 350ms, then restores.</x:v>
@@ -11885,7 +11883,7 @@
         <x:v>Build the Frozen Diamond Jackpot with both drop banks. Any right drop starts a moving one-saucer shipment window. Complete/reset the right bank, then hit the first post-reset right drop to expand the moving window to two saucers; repeat to reach three.</x:v>
       </x:c>
       <x:c r="G21" s="31" t="str">
-        <x:v>Collect one correct saucer shipment, or two with More Jackpots; otherwise stops on ball end. A terminal saucer remains held until the villain summary ends.</x:v>
+        <x:v>Collect three correct saucer shipments, or four with More Jackpots; otherwise stops on ball end. A terminal saucer remains held until the villain summary ends.</x:v>
       </x:c>
       <x:c r="H21" s="31" t="str">
         <x:v>Drops score 25K and bank 25K Diamond Bonus. Base Jackpot is 100K; right drops add 25K and left drops add 40K. Bigger uses 200K/+50K/+75K. Wrong saucer scores 10K. STAR banks 100K and freezes the current available window for 10s/15s.</x:v>
@@ -12112,16 +12110,16 @@
         </x:is>
       </x:c>
       <x:c r="F27" s="31" t="str">
-        <x:v>Find the correct shot among three choices and collect three Hypnosis Jackpots before the available chances expire.</x:v>
+        <x:v>Find the correct shot among three flashing choices. The spinner reveals the answer; four correct Hypnosis Jackpots defeat Pardo.</x:v>
       </x:c>
       <x:c r="G27" s="31" t="str">
-        <x:v>Third correct shot defeats Pardo; fewer than three correct after five chances (seven with More JP) lets him escape.</x:v>
+        <x:v>Four correct Jackpots defeat Pardo. Four base rounds are available; More Jackpots adds two recovery rounds.</x:v>
       </x:c>
       <x:c r="H27" s="31" t="str">
-        <x:v>Spinner reveals the correct choice for 4 seconds (6 seconds with More Time). Correct Jackpots start at 100K and increase 50K; Bigger JP starts at 150K and increases 75K. Wrong choices score 10K and consume the chance.</x:v>
+        <x:v>Normal clean Jackpot ladder: 200K/300K/400K/500K. One wrong choice reduces the current Jackpot by 100K. Bigger uses 300K/450K/600K/750K with a 150K first-wrong reduction. Every wrong choice scores 20K. Reveal is 4s, or 6s with More Time.</x:v>
       </x:c>
       <x:c r="I27" s="31" t="str">
-        <x:v>Seven logical shot groups; three are selected per chance. Upper-left, upper-center, and upper-right targets are one grouped choice and always share the same good/bad state. Hidden choices are solid green across white and green lenses. Reveal flashes only the correct choice green and turns wrong choices off. Result GI restores after a 350ms green/red confirmation. Shot Assist makes all three choices correct on the first chance. Summary outcome distinguishes defeat from escape.</x:v>
+        <x:v>Seven logical shot groups; three selected per round. Upper-left/center/right targets are one grouped choice. Available choices flash green identically; first wrong goes dark and the two survivors continue flashing. Spinner reveal flashes only the correct choice and turns wrong choices off. Shot Assist makes all three choices correct in Round 1. Summary stats are 1ST-GUESS JPs and 2ND-GUESS JPs.</x:v>
       </x:c>
     </x:row>
     <x:row r="28">

--- a/docs/ASM67_55_Villains_11_Wizards_1_Final_Wizard_Tracker.xlsx
+++ b/docs/ASM67_55_Villains_11_Wizards_1_Final_Wizard_Tracker.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R5e89322b57934766"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R6f4760134a0a47b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R8e9588920f084747"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R43421266426f4323"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R078df61baac64514"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R6d868e37bab54ae3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Rf97cb9494d234408"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R04dde9cca1cb42da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R4416ec132511442d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R5a47c0d7efb34093"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Rcfe088a08840494a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="Rcfba3874cbbb4679"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R6ddcb59ede384b2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rc15563cc366a45d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Rcb48084f83934f24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="Ref5787e6098049dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R88cf85b24a634a48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R665d7239060c4d42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R3512c3331cc34379"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R063b5a35b1f74514"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R9a0ed0fa7ba94b5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R20dce9fe8f084082"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R0551c8de669a4645"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Ref30b921f7bc4abb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="Rac489fc127304a0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R7128a9b49bde4212"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1286,7 +1286,7 @@
         </x:is>
       </x:c>
       <x:c r="E7" s="31" t="str">
-        <x:v>Implemented / needs lighting playtest</x:v>
+        <x:v>Implemented / reviewed; 20s right-bank rooftop route needs machine test</x:v>
       </x:c>
       <x:c r="F7" s="31" t="inlineStr">
         <x:is>
@@ -1324,7 +1324,7 @@
         </x:is>
       </x:c>
       <x:c r="M7" s="31" t="str">
-        <x:v>State-management mode; bright-blue rollover states and the conditional left-bank GI now make the required arm-lock shots explicit.</x:v>
+        <x:v>State-management mode; bright-blue rollover states and the conditional left-bank GI now make the required arm-lock shots explicit. The right bank now creates a 20-second routing tradeoff: spinner shots still build the Web Jackpot but travel through the VUK to the roof, temporarily bypassing lower arm-release shots.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -2023,7 +2023,7 @@
         </x:is>
       </x:c>
       <x:c r="E20" s="31" t="str">
-        <x:v>Implemented / recent Ox chase lighting fix / needs playtest</x:v>
+        <x:v>Implemented / VUK route and Ox chase lighting update / needs playtest</x:v>
       </x:c>
       <x:c r="F20" s="31" t="inlineStr">
         <x:is>
@@ -2057,7 +2057,7 @@
         <x:v>Three rooftop jackpots, then center-web Ox Super / ball end</x:v>
       </x:c>
       <x:c r="M20" s="31" t="str">
-        <x:v>Team/zone buildup role. Ox-ready lighting now uses the approved four-insert 80F0F0 chase at 300ms per step and explicitly clears l_special with the other chase inserts; gameplay and scoring are unchanged.</x:v>
+        <x:v>Team/zone buildup role. A F0D040 shared VUK chase now guides rooftop entry from the first lit upper jackpot until the third is collected. The existing 80F0F0 center-web Ox chase then takes over. Gameplay and scoring are unchanged.</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -2127,7 +2127,7 @@
         </x:is>
       </x:c>
       <x:c r="E22" s="31" t="str">
-        <x:v>Implemented / recent control-lighting repair / physical congestion test pending</x:v>
+        <x:v>Implemented / reviewed; gate-synchronized VUK chase needs machine test</x:v>
       </x:c>
       <x:c r="F22" s="31" t="inlineStr">
         <x:is>
@@ -2161,7 +2161,7 @@
         <x:v>Multiball reaches one ball / ball end</x:v>
       </x:c>
       <x:c r="M22" s="31" t="str">
-        <x:v>Chapter 5 controlled area-building multiball. Autoplunge, paired left-sling lamps, area-show lifecycle, held-lamp cleanup, and single-owner saucer release are repaired. Same-saucer physical congestion still requires a separately approved machine-tested strategy.</x:v>
+        <x:v>Area-control multiball with repeatable VUK cashouts. The directional chase now follows the rooftop gate state rather than Jackpot-ready state, remaining on through the delayed kick and stopping when the gate closes.</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -2335,43 +2335,33 @@
         </x:is>
       </x:c>
       <x:c r="E26" s="31" t="str">
-        <x:v>Implemented / recent retry-rule fix</x:v>
+        <x:v>Implemented / starting-ball ownership repair / needs machine playtest</x:v>
       </x:c>
       <x:c r="F26" s="31" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">1</x:t>
         </x:is>
       </x:c>
-      <x:c r="G26" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Memory sequence</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H26" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Audio-visual Simon Says</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I26" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Left web + bank rubbers + center web</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J26" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Incrementing correct-note jackpots</x:t>
-        </x:is>
+      <x:c r="G26" s="31" t="str">
+        <x:v>Memory sequence</x:v>
+      </x:c>
+      <x:c r="H26" s="31" t="str">
+        <x:v>Saucer-started randomized musical patterns</x:v>
+      </x:c>
+      <x:c r="I26" s="31" t="str">
+        <x:v>Left web + left-bank rubber + right pop + right-bank rubber</x:v>
+      </x:c>
+      <x:c r="J26" s="31" t="str">
+        <x:v>250K per correct note; 300K with Bigger Jackpots</x:v>
       </x:c>
       <x:c r="K26" s="31" t="str">
-        <x:v>Startup and demonstration input lock prevents drop-knockdown vibration or live-ball switches from being judged before the response phase. Three mistakes are allowed per mode.</x:v>
+        <x:v>Patterns grow 1 -&gt; 2 -&gt; 3 -&gt; 4 notes and then remain at four; clean saucer returns replay the current pattern once</x:v>
       </x:c>
       <x:c r="L26" s="31" t="str">
-        <x:v>Complete Round 3 (or Round 4 with More Jackpots), or escape on the third mistake</x:v>
-      </x:c>
-      <x:c r="M26" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Completes Chapter 5 with a memory-and-precision identity unlike Harley multiball, Conquistador routing, Spider-Slayer hunting, or Metal Monster rescue pressure.</x:t>
-        </x:is>
+        <x:v>Three failed rounds, or four with More Jackpots / ball end</x:v>
+      </x:c>
+      <x:c r="M26" s="31" t="str">
+        <x:v>Musical-memory role. A starting lower saucer or Mystery VUK is inherited from the villain intro and held through the first WATCH presentation; the owning device ejects for REPEAT. Completing one pattern defeats Fiddler for progression, while play continues until the failure limit.</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -2607,10 +2597,8 @@
           <x:t xml:space="preserve">Infinata</x:t>
         </x:is>
       </x:c>
-      <x:c r="E31" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs playtest</x:t>
-        </x:is>
+      <x:c r="E31" s="31" t="str">
+        <x:v>Implemented / reviewed; white saucer-hole pulse needs machine test</x:v>
       </x:c>
       <x:c r="F31" s="31" t="inlineStr">
         <x:is>
@@ -2647,10 +2635,8 @@
           <x:t xml:space="preserve">Super / timer / ball end</x:t>
         </x:is>
       </x:c>
-      <x:c r="M31" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Three required areas; optional fourth with More Jackpots.</x:t>
-        </x:is>
+      <x:c r="M31" s="31" t="str">
+        <x:v>Three required areas; optional fourth with More Jackpots. Super guidance uses a synchronized four-level white brightness pulse on all six saucer-hole lamps and no numbered inserts.</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -3040,10 +3026,8 @@
           <x:t xml:space="preserve">Doctor Zapp</x:t>
         </x:is>
       </x:c>
-      <x:c r="E38" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs playtest</x:t>
-        </x:is>
+      <x:c r="E38" s="31" t="str">
+        <x:v>Implemented / reviewed; independent bank-lighting fix needs machine test</x:v>
       </x:c>
       <x:c r="F38" s="31" t="inlineStr">
         <x:is>
@@ -3080,10 +3064,8 @@
           <x:t xml:space="preserve">25 flashes / ball end</x:t>
         </x:is>
       </x:c>
-      <x:c r="M38" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Distinct from Electro: fixed rooftop camera-flash objective with helper targets rather than a travelling playfield spark.</x:t>
-        </x:is>
+      <x:c r="M38" s="31" t="str">
+        <x:v>Distinct from Electro: fixed rooftop camera-flash objective with helper targets rather than a travelling playfield spark. Bank cues now use explicit priority so the remaining unhit bank stays pulsing until qualified, then both clear for rooftop play.</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -7682,10 +7664,10 @@
         </x:is>
       </x:c>
       <x:c r="G7" s="31" t="str">
-        <x:v>Implemented / needs lighting playtest</x:v>
+        <x:v>Implemented / reviewed; 20s right-bank rooftop route needs machine test</x:v>
       </x:c>
       <x:c r="H7" s="31" t="str">
-        <x:v>Rollovers lock arms; completing the left bank locks one arm and relights the web jackpot; spinner boosts the multiplier. Every collected web jackpot adds 100K to persistent doc_ock_bonus as BREAKOUT BONUS. Free-arm lane rollovers pulse bright blue, locked-arm rollovers stay solid blue, and the left-bank GI pulses blue while any arm remains free.</x:v>
+        <x:v>Rollovers lock arms; completing the left bank locks one arm and relights the web jackpot; spinner boosts the multiplier. Every collected web jackpot adds 100K to persistent doc_ock_bonus as BREAKOUT BONUS. Free-arm lane rollovers pulse bright blue, locked-arm rollovers stay solid blue, and the left-bank GI pulses blue while any arm remains free. Completing the right bank opens rooftop access for a full 20 seconds; another completion restarts the window. Spinner shots continue through the VUK to the roof, bypassing lower arm-release shots. The right-bank GI matches the left-bank blue pulse while access is closed, and a blue VUK chaser runs throughout the open window.</x:v>
       </x:c>
       <x:c r="I7" s="31" t="inlineStr">
         <x:is>
@@ -8242,10 +8224,10 @@
         </x:is>
       </x:c>
       <x:c r="G20" s="31" t="str">
-        <x:v>Implemented / recent Ox chase lighting fix / needs playtest</x:v>
+        <x:v>Implemented / VUK route and Ox chase lighting update / needs playtest</x:v>
       </x:c>
       <x:c r="H20" s="31" t="str">
-        <x:v>Left drops, pops, and right drops build the matching upper-target jackpots; continued zone hits build 1X-5X multipliers. Upper-spinner spins score 5K and add 50K to Ox; collected rooftop jackpots also add their awards. All three rooftop jackpots light the center-web Ox Super. Ox-ready lighting now chases l_mid_multibonus -&gt; l_advance_multiplier -&gt; l_special -&gt; l_mid_web_target at 300ms per step in 80F0F0, with all four inserts explicitly cleared on teardown.</x:v>
+        <x:v>Left drops, pops, and right drops build the matching upper-target jackpots; continued zone hits build 1X-5X multipliers. Upper-spinner spins score 5K and add 50K to Ox; collected rooftop jackpots also add their awards. The first lit rooftop jackpot starts the F0D040 shared VUK/roof-entry chase. It remains active while rooftop jackpots remain, then stops when the third is collected and the existing 80F0F0 center-web Ox chase takes over.</x:v>
       </x:c>
       <x:c r="I20" s="31" t="inlineStr">
         <x:is>
@@ -8326,10 +8308,10 @@
         </x:is>
       </x:c>
       <x:c r="G22" s="31" t="str">
-        <x:v>Implemented / recent control-lighting repair / physical congestion test pending</x:v>
+        <x:v>Implemented / reviewed; gate-synchronized VUK chase needs machine test</x:v>
       </x:c>
       <x:c r="H22" s="31" t="str">
-        <x:v>Controlled 2-ball area multiball: delayed autoplunge Ball 2, capture one ball in a red-hole-lit saucer, then light eight independent areas at 50K each. Four areas qualify the repeatable VUK Jackpot at 100K per area, or 150K with Bigger; the full award also banks to HARLEY JACKPOTS. The paired upper/lower left-sling GI now acts as one area. Area guidance starts only after a lock and clears between rounds; More Jackpots retains two areas internally until the next lock. Held-saucer lights and eject ownership now clean up exactly once. Occupied-saucer congestion remains an unresolved machine-test issue with no automatic rescue added.</x:v>
+        <x:v>Two-ball area-lighting multiball. Lock one ball in a saucer, light at least four areas, then collect repeatable VUK Jackpots. The A0A0F0 shared route chase now starts only when Harley opens the rooftop gate and stops exactly when Harley closes it after upper entry, fallback, startup cleanup, or teardown.</x:v>
       </x:c>
       <x:c r="I22" s="31" t="inlineStr">
         <x:is>
@@ -8494,10 +8476,10 @@
         </x:is>
       </x:c>
       <x:c r="G26" s="31" t="str">
-        <x:v>Implemented / recent retry-rule fix</x:v>
+        <x:v>Implemented / starting-ball ownership repair / needs machine playtest</x:v>
       </x:c>
       <x:c r="H26" s="31" t="str">
-        <x:v>Simon Says violin mode. Three normal rounds use one, two, and three unique notes; More Jackpots adds a four-note encore. Each note flashes its ordered pulse pattern four times, then stays solid. Input is locked during startup drop knockdowns, setup delays, demonstrations, and replay delays. The first two mistakes restart the current round and replay the full pattern after 1.5s; the third mistake ends the mode. Shot Assist forgives the first wrong input without consuming a mistake.</x:v>
+        <x:v>Musical-memory mode using Left Web, Left Bank rubber, Right Pop, and Right Bank rubber. A lower-saucer start holds that ball through the intro and first WATCH presentation. A Mystery/VUK start cancels the normal VUK eject, holds the VUK ball through WATCH, then fires it for REPEAT. Patterns grow from one note to four, then continue as new four-note patterns until three failures, or four with More Jackpots. Correct notes score 250K, or 300K with Bigger.</x:v>
       </x:c>
       <x:c r="I26" s="31" t="inlineStr">
         <x:is>
@@ -8703,15 +8685,11 @@
           <x:t xml:space="preserve">Infinata</x:t>
         </x:is>
       </x:c>
-      <x:c r="G31" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs playtest</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H31" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">One green creature area lights at a time from pops, left drops, right drops, ...</x:t>
-        </x:is>
+      <x:c r="G31" s="31" t="str">
+        <x:v>Implemented / reviewed; white saucer-hole pulse needs machine test</x:v>
+      </x:c>
+      <x:c r="H31" s="31" t="str">
+        <x:v>One green creature area lights at a time from pops, left drops, right drops, ... During the Super phase, all six saucer-hole lamps breathe together through 404040, 808080, FFFFFF, and 808080 at 250ms per step; the green 1/2/3 number inserts remain off.</x:v>
       </x:c>
       <x:c r="I31" s="31" t="inlineStr">
         <x:is>
@@ -9015,15 +8993,11 @@
           <x:t xml:space="preserve">Doctor Zapp</x:t>
         </x:is>
       </x:c>
-      <x:c r="G38" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented / needs playtest</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H38" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Camera Flash mode: qualify both lower banks, then use the rooftop spinner and unique upper-target boosts to reach 25 flashes. More Jackpots adds a 10-second bonus-spin window.</x:t>
-        </x:is>
+      <x:c r="G38" s="31" t="str">
+        <x:v>Implemented / reviewed; independent bank-lighting fix needs machine test</x:v>
+      </x:c>
+      <x:c r="H38" s="31" t="str">
+        <x:v>Camera Flash mode: qualify both lower banks, then use the rooftop spinner and unique upper-target boosts to reach 25 flashes. More Jackpots adds a 10-second bonus-spin window. During qualification, each bank cue has independent priority: hitting one bank turns only that bank solid while the opposite bank continues pulsing until hit. Both bank cues stop when rooftop access opens.</x:v>
       </x:c>
       <x:c r="I38" s="31" t="inlineStr">
         <x:is>
@@ -11335,7 +11309,7 @@
         </x:is>
       </x:c>
       <x:c r="I7" s="31" t="str">
-        <x:v>Persistent arm-lock, web-jackpot, and breakout progress. Free-arm lane rollovers pulse bright blue; locked-arm rollovers stay solid blue. Left-bank GI pulses slowly in blue while any arm remains free and stops when all four are locked.</x:v>
+        <x:v>Persistent arm-lock, web-jackpot, and breakout progress. Free-arm lane rollovers pulse bright blue; locked-arm rollovers stay solid blue. Left-bank GI pulses slowly in blue while any arm remains free and stops when all four are locked. Right-bank completion now opens a restartable 20-second rooftop window. Upper entry does not close it; VUK entry ejects upstairs. The right-bank GI uses the left bank's blue pulse while closed, and the shared blue route chase remains active for the full open window.</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -11852,7 +11826,7 @@
         <x:v>Zone hits score 25K. Rooftop jackpots start at 100K, or 150K with Bigger, and use the zone multiplier. Spinner spins score 5K and add 50K to Ox; collected rooftop jackpots also add their awards.</x:v>
       </x:c>
       <x:c r="I20" s="31" t="str">
-        <x:v>Recent Ox chase lighting fix; needs machine playtest. Ox-ready chase order is l_mid_multibonus -&gt; l_advance_multiplier -&gt; l_special -&gt; l_mid_web_target, 300ms per step in 80F0F0. All four chase inserts are explicitly cleared when the chase or mode stops.</x:v>
+        <x:v>VUK route and Ox chase lighting update; needs machine playtest. The F0D040 shared VUK chase starts when the first rooftop jackpot opens the gate, remains active while rooftop jackpots remain, and stops when the third is collected. The existing 80F0F0 center-web Ox chase then takes over. Both chases are explicitly stopped during cleanup; gameplay and scoring are unchanged.</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -11926,7 +11900,7 @@
         <x:v>Saucer capture and each unique area score 50K. VUK Jackpots are 100K per lit area, or 150K with Bigger, and add their full value to persistent HARLEY JACKPOTS. More Jackpots retains two areas for the next lock.</x:v>
       </x:c>
       <x:c r="I22" s="31" t="str">
-        <x:v>Recent control/lighting repair; needs machine testing. Multiball now sets and clears the shared delayed-autoplunge flag; paired left-sling GI acts together; build/clear events drive area shows; held-saucer lamps stop on release; explicit ownership prevents duplicate stop-time eject requests. Physical same-saucer congestion remains unresolved and no rescue behavior was added.</x:v>
+        <x:v>A0A0F0 shared VUK route chase is synchronized to Harley's physical gate lifecycle: gate open starts it; every gate close stops it. Spinner readiness remains separate. Needs machine test.</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -12073,16 +12047,16 @@
         </x:is>
       </x:c>
       <x:c r="F26" s="31" t="str">
-        <x:v>Watch each ordered violin pattern, then repeat it using Left Web, Left Bank rubber, Center Web, and Right Bank rubber.</x:v>
+        <x:v>Enter a saucer to watch a randomized violin pattern, then repeat it using Left Web, Left Bank rubber, Right Pop, and Right Bank rubber. Successful patterns grow from one note to four; later patterns remain four notes.</x:v>
       </x:c>
       <x:c r="G26" s="31" t="str">
-        <x:v>Complete three rounds, or four with More Jackpots. Three mistakes during the mode allow Fiddler to escape.</x:v>
+        <x:v>Completing the first pattern defeats Fiddler for progression, but play continues until three failed rounds, or four with More Jackpots; otherwise the attempt stops on ball end.</x:v>
       </x:c>
       <x:c r="H26" s="31" t="str">
-        <x:v>Patterns contain one to four unique notes. Correct-note scoring remains 100K; 200K/300K; 400K/500K/600K; and 700K/800K/900K/1M in the optional encore.</x:v>
+        <x:v>Each correct note scores 250K, or 300K with Bigger Jackpots. A clean saucer return replays the current pattern once without erasing correct-note progress.</x:v>
       </x:c>
       <x:c r="I26" s="31" t="str">
-        <x:v>Inputs are ignored until PLAY THE PATTERN. A non-terminal wrong note replays the complete current pattern after 1.5s. Shot Assist forgives the first wrong input and does not consume a mistake.</x:v>
+        <x:v>Starting-ball ownership repaired; needs machine playtest. A lower-saucer start retains that ball through intro/WATCH. A Mystery/VUK start cancels Mystery and shared eject requests, retains the VUK ball through WATCH, then fires the VUK for REPEAT. Starts with neither device occupied retain the normal saucer prompt.</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -12278,10 +12252,8 @@
           <x:t xml:space="preserve">Area awards 200K, 300K, 400K; Super 1M. Bigger increases values; More Time makes the Super 30s. VUK routes use the shared 1.5-second eject while Infinata owns the mode.</x:t>
         </x:is>
       </x:c>
-      <x:c r="I31" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">More Jackpots adds an optional fourth area during the Super; Safety Net ball save; Shot Assist awards the active and next areas.</x:t>
-        </x:is>
+      <x:c r="I31" s="31" t="str">
+        <x:v>More Jackpots adds an optional fourth area during the Super; Safety Net ball save; Shot Assist awards the active and next areas. Any-saucer Super guidance now breathes only the six hole lamps through 404040, 808080, FFFFFF, and 808080 at 250ms per step; green number inserts are unused.</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -12579,10 +12551,8 @@
           <x:t xml:space="preserve">Drops score 100K, upper helpers score 50K, and each flash scores 50K. More Jackpots adds a timed bonus-spin window after completion.</x:t>
         </x:is>
       </x:c>
-      <x:c r="I38" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Implemented with custom code, YAML, widget, lighting, status and summary variables; needs on-machine playtest.</x:t>
-        </x:is>
+      <x:c r="I38" s="31" t="str">
+        <x:v>Implemented with custom code, YAML, widget, lighting, status and summary variables; needs on-machine playtest. Drop-bank qualification lighting is independent: the completed bank turns solid and the unhit bank keeps pulsing until its own first hit; both cues clear at rooftop access.</x:v>
       </x:c>
     </x:row>
     <x:row r="39">

--- a/docs/ASM67_55_Villains_11_Wizards_1_Final_Wizard_Tracker.xlsx
+++ b/docs/ASM67_55_Villains_11_Wizards_1_Final_Wizard_Tracker.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rc15563cc366a45d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Rcb48084f83934f24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="Ref5787e6098049dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R88cf85b24a634a48"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R665d7239060c4d42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R3512c3331cc34379"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R063b5a35b1f74514"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R9a0ed0fa7ba94b5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R20dce9fe8f084082"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R0551c8de669a4645"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Ref30b921f7bc4abb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="Rac489fc127304a0a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R7128a9b49bde4212"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R577f5063c1424653"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Rb78b5da84916494c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="Rf8ddf1207e7f411a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R4aad6d1e67b44403"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Rcbc240de532f4271"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Rbc7045f4109642ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Rbe51306fc7c245d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R81e58da296bb412d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Rc6ac95a55dc9403c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R2f5e92ee87a6499a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Rae56216b45f8419e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="Rfae4cb7ac8d84e23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="Raab6976be78c4010"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -9538,10 +9538,8 @@
           <x:t xml:space="preserve">Implemented / needs playtest</x:t>
         </x:is>
       </x:c>
-      <x:c r="H50" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Complete all eight lower drops in strict left-to-right order. Each upper-spinner spin drops the next required target; the player may advance directly only by hitting that same target. A wrong direct hit resets only that bank, then restores completed targets after 200ms with 200ms staged re-drops. Correct drops score 100K. Completing all eight lights a 15s center-web Super for 500K; expiry ends the one allowed attempt.</x:t>
-        </x:is>
+      <x:c r="H50" s="31" t="str">
+        <x:v>Complete all eight lower drops in strict left-to-right order. Each upper-spinner spin drops the next required target; the player may advance directly only by hitting that same target. A wrong direct hit resets only that bank, then restores completed targets after 200ms with 200ms staged re-drops. Correct drops score 100K. Completing all eight lights a 20s center-web Super for 500K; expiry ends the one allowed attempt. More Time extends the Super window to 25s.</x:v>
       </x:c>
       <x:c r="I50" s="31" t="inlineStr">
         <x:is>
@@ -13049,15 +13047,11 @@
       <x:c r="F50" s="31" t="str">
         <x:v>Complete left 1-3, then right 1-5 in order. After the startup bank reset, the rooftop gate opens and remains open while the upper spinner is needed; each spin drops the next target. A correct direct hit also advances. A wrong direct hit resets only that bank and restores its completed targets after 200ms, with 200ms staged re-drops.</x:v>
       </x:c>
-      <x:c r="G50" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">After all eight drops, the center web is lit for 15s. Center Super defeats Skymaster. Expiry ends the mode unsuccessfully with no second attempt. More Jackpots also lights the left web; each web can score once.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H50" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Correct drops 100K; center/left web Supers 500K. Bigger: 150K drops and 750K Supers. More Time: 20s. Safety: opening 10s save. Assist: first upper spin advances two drops.</x:t>
-        </x:is>
+      <x:c r="G50" s="31" t="str">
+        <x:v>After all eight drops, the center web is lit for 20s. Center Super defeats Skymaster. Expiry ends the mode unsuccessfully with no second attempt. More Jackpots also lights the left web; each web can score once.</x:v>
+      </x:c>
+      <x:c r="H50" s="31" t="str">
+        <x:v>Correct drops 100K; center/left web Supers 500K. Bigger: 150K drops and 750K Supers. More Time: 25s. Safety: opening 10s save. Assist: first upper spin advances two drops.</x:v>
       </x:c>
       <x:c r="I50" s="31" t="str">
         <x:v>Implemented with all eight physical drop coils, programmatic-switch guards, strict direct-hit validation, 200ms bank restoration staging, explicit ordered-phase rooftop gate ownership, VUK shared eject handling, gate closure for the Web Super and mode stop, target/web lighting, one-attempt timer, Case Files, status, and summary values; needs on-machine playtest.</x:v>

--- a/docs/ASM67_55_Villains_11_Wizards_1_Final_Wizard_Tracker.xlsx
+++ b/docs/ASM67_55_Villains_11_Wizards_1_Final_Wizard_Tracker.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R577f5063c1424653"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Rb78b5da84916494c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="Rf8ddf1207e7f411a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R4aad6d1e67b44403"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Rcbc240de532f4271"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Rbc7045f4109642ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Rbe51306fc7c245d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R81e58da296bb412d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Rc6ac95a55dc9403c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R2f5e92ee87a6499a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Rae56216b45f8419e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="Rfae4cb7ac8d84e23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="Raab6976be78c4010"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R5009715350984401"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R81f3362f526042a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R8dbac9c2fe23481c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="Rbc5eca579f3f4a1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R55a416502bc14687"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Red00f9f479dc423e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Ra7c50e6d665c4a30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Rb276d363099f4086"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R128807cc11b849ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Rd1a7538ae97f439b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R7b4dba70370a4bef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="Rc8bfe6ba1e9d4b38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="Rf78e46a40b4847c3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4846,10 +4846,8 @@
           <x:t xml:space="preserve">The Web Tightens</x:t>
         </x:is>
       </x:c>
-      <x:c r="E6" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Placeholder shell — full design/coding required</x:t>
-        </x:is>
+      <x:c r="E6" s="31" t="str">
+        <x:v>Approved/coded — needs playtest</x:v>
       </x:c>
       <x:c r="F6" s="85" t="n"/>
       <x:c r="G6" s="85" t="n"/>
@@ -10043,15 +10041,11 @@
           <x:t xml:space="preserve">start_mode_the_web_tightens</x:t>
         </x:is>
       </x:c>
-      <x:c r="F6" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">No individual Case File powers. Each Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files; 0–500K). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G6" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Explicit placeholder shell; full design and coding required.</x:t>
-        </x:is>
+      <x:c r="F6" s="31" t="str">
+        <x:v>No individual Case File powers. Each 1X phase Jackpot = 100K + 20K × the chapter's collected Case Files (0–25 files; +0–500K). 2X phase Jackpots double both base and prep. The rooftop Super is separate at 1M × successful phases and does not receive Wizard Prep.</x:v>
+      </x:c>
+      <x:c r="G6" s="31" t="str">
+        <x:v>Approved/coded from the 2026-09-01 design: repeating 2-ball/VUK-lock wizard with Fiddler, Metal-Eating Monster, Conquistador, Spider-Slayer, and Harley &amp; Clivendon phases; saucers park excess balls; Chapter Case Files add 20K to every 1X phase JP; phase wins build a 1M-per-success rooftop Super. Needs machine playtest and polish.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -13545,10 +13539,8 @@
           <x:t xml:space="preserve">Playtest coded mini-wizards</x:t>
         </x:is>
       </x:c>
-      <x:c r="C2" s="45" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Sinister Surge and Trubble Unleashed are approved/coded. Mastermind Trap, Crime Wave, and Fifth Dimension Curse are functional but provisional and require design approval as well as playtest.</x:t>
-        </x:is>
+      <x:c r="C2" s="45" t="str">
+        <x:v>Sinister Surge, Trubble Unleashed, and The Web Tightens are approved/coded. Mastermind Trap, Crime Wave, and Fifth Dimension Curse are functional but provisional and require design approval as well as playtest.</x:v>
       </x:c>
       <x:c r="D2" s="45" t="inlineStr">
         <x:is>
@@ -13795,10 +13787,8 @@
           <x:t xml:space="preserve">Finish mini-wizard and final-wizard designs</x:t>
         </x:is>
       </x:c>
-      <x:c r="C14" s="45" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Review 3 functional/provisional mini-wizards; fully design and code 6 placeholder shells; complete the dedicated Kingpin Final Showdown design/retheme. Wizard Case Files add only 20K each to Jackpot/Super Jackpot values (max +500K).</x:t>
-        </x:is>
+      <x:c r="C14" s="45" t="str">
+        <x:v>Review 3 functional/provisional mini-wizards; fully design and code 5 remaining placeholder shells; complete the dedicated Kingpin Final Showdown design/retheme. The Web Tightens is approved/coded and needs machine playtest. Wizard Case Files add 20K each to qualifying Jackpot values (max +500K per 1X JP).</x:v>
       </x:c>
       <x:c r="D14" s="45" t="inlineStr">
         <x:is>

--- a/docs/ASM67_55_Villains_11_Wizards_1_Final_Wizard_Tracker.xlsx
+++ b/docs/ASM67_55_Villains_11_Wizards_1_Final_Wizard_Tracker.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R5009715350984401"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R81f3362f526042a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R8dbac9c2fe23481c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="Rbc5eca579f3f4a1f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R55a416502bc14687"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Red00f9f479dc423e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Ra7c50e6d665c4a30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Rb276d363099f4086"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R128807cc11b849ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Rd1a7538ae97f439b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R7b4dba70370a4bef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="Rc8bfe6ba1e9d4b38"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="Rf78e46a40b4847c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R88c0d65645a04647"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R7cceebe8494545cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R9858b8b3a2de4f53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R200a28cd274a4847"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R6128c5b3700a4feb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Rb37a130f22ce43b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Rad88e0472a93495c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Red4dfe5e86754295"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R65e4513eb899455d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Rce5f05f276754c83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R75796648cadc42fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="Ref5bf6f925a94378"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R025df34039ce473d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -9626,10 +9626,8 @@
           <x:t xml:space="preserve">Implemented — needs playtest</x:t>
         </x:is>
       </x:c>
-      <x:c r="H52" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Knight Must Fall: 3 rooftop score-attack rounds (4 with More Jackpots). Each 100K upper exit stages the opposite drop bank; an 8s/12s window begins on post drop or the physical right inlane. One physical target scores, then the bank collapses center-out in 500ms steps. VUK or timeout triggers the same no-score collapse. Gate remains open.</x:t>
-        </x:is>
+      <x:c r="H52" s="31" t="str">
+        <x:v>Knight Must Fall: 3 rooftop score-attack rounds (4 with More Jackpots). Each 100K upper exit stages the opposite drop bank; an 8s/12s window begins on post drop or the physical right inlane. One physical target scores, then the bank collapses center-out in 500ms steps. VUK or timeout triggers the same no-score collapse. Gate remains open. Upper entry changes the prompt to EXIT LEFT OR RIGHT and pulses both upper-exit GI lamps until an exit is selected.</x:v>
       </x:c>
       <x:c r="I52" s="31" t="inlineStr">
         <x:is>

--- a/docs/ASM67_55_Villains_11_Wizards_1_Final_Wizard_Tracker.xlsx
+++ b/docs/ASM67_55_Villains_11_Wizards_1_Final_Wizard_Tracker.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R88c0d65645a04647"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R7cceebe8494545cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R9858b8b3a2de4f53"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R200a28cd274a4847"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R6128c5b3700a4feb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Rb37a130f22ce43b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Rad88e0472a93495c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Red4dfe5e86754295"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R65e4513eb899455d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Rce5f05f276754c83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R75796648cadc42fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="Ref5bf6f925a94378"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R025df34039ce473d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R473a536312b44f7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R3d76a2671dd64356"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R23bc86742f6d4bf5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R5f6517ccc24048a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R8119b5e63cf245b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R3ce2bbb22eda4524"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Reb1cf4162c9741ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Rab62ab6def1a4b2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Rb0c775df06874376"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R090ebaedf6474bcc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R8b3956aa187445fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R6df9b7d243b447ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R7c633ec0ec874d17"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -10015,7 +10015,7 @@
         </x:is>
       </x:c>
     </x:row>
-    <x:row r="6">
+    <x:row r="6" ht="132" hidden="0" customHeight="1">
       <x:c r="A6" s="31" t="n">
         <x:v>5</x:v>
       </x:c>
@@ -10043,7 +10043,7 @@
         <x:v>No individual Case File powers. Each 1X phase Jackpot = 100K + 20K × the chapter's collected Case Files (0–25 files; +0–500K). 2X phase Jackpots double both base and prep. The rooftop Super is separate at 1M × successful phases and does not receive Wizard Prep.</x:v>
       </x:c>
       <x:c r="G6" s="31" t="str">
-        <x:v>Approved/coded from the 2026-09-01 design: repeating 2-ball/VUK-lock wizard with Fiddler, Metal-Eating Monster, Conquistador, Spider-Slayer, and Harley &amp; Clivendon phases; saucers park excess balls; Chapter Case Files add 20K to every 1X phase JP; phase wins build a 1M-per-success rooftop Super. Needs machine playtest and polish.</x:v>
+        <x:v>Approved/coded from the 2026-09-01 design: repeating 2-ball/VUK-lock wizard with Fiddler, Metal-Eating Monster, Conquistador, Spider-Slayer, and Harley &amp; Clivendon phases; saucers park excess balls; Chapter Case Files add 20K to every 1X phase JP; phase wins build a 1M-per-success rooftop Super. Needs machine playtest and polish. Fiddler parity update: both drop banks stage down during GET READY; individual drop switches are ignored; the exposed left/right bank rubbers are the bank-note inputs; WATCH strobe, note gaps, repeat pause, and correct/wrong feedback match standalone Fiddler.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">

--- a/docs/ASM67_55_Villains_11_Wizards_1_Final_Wizard_Tracker.xlsx
+++ b/docs/ASM67_55_Villains_11_Wizards_1_Final_Wizard_Tracker.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R473a536312b44f7d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R3d76a2671dd64356"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R23bc86742f6d4bf5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R5f6517ccc24048a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R8119b5e63cf245b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R3ce2bbb22eda4524"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Reb1cf4162c9741ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Rab62ab6def1a4b2c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="Rb0c775df06874376"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R090ebaedf6474bcc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R8b3956aa187445fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R6df9b7d243b447ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R7c633ec0ec874d17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R34f31d7c8aab4a10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Rea01e5faef9f4f61"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R4658386001564602"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R71bad4fed899403c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Ref9a1f1d09734add"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R5ae247d37f9a47ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="Rdd8adb27d024428d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="Rf269164e7ae3430f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R99b7be21bbcf4bc1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Reb8b6bad867c43bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="R5783142f535948cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R4e4cfa79d51649ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Music Inventory" sheetId="13" r:id="R815fd955cc344958"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -10103,15 +10103,11 @@
           <x:t xml:space="preserve">start_mode_mad_science_meltdown</x:t>
         </x:is>
       </x:c>
-      <x:c r="F8" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">No individual Case File powers. Each Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files; 0–500K). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G8" s="31" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Explicit placeholder shell; full design and coding required.</x:t>
-        </x:is>
+      <x:c r="F8" s="31" t="str">
+        <x:v>No individual Case File powers. Every Gas and Noah Jackpot adds 20K × the chapter's collected Case Files (0–25 files; 0–500K). Red/yellow gas awards, upper-spinner build increments, and the 1M four-ball Magneto award do not receive this bonus.</x:v>
+      </x:c>
+      <x:c r="G8" s="31" t="str">
+        <x:v>Approved/coded: repeating 3-ball multiball with 20s opening save. Each left drop releases one independent gas zone; lower-spinner hits cool all active zones red → yellow → green; green collects a 500K+ Case File Gas Jackpot. Upper targets and early right-drop hits eliminate Noah's false locations; the last standing right target collects a 500K+ Case File + 100K-per-upper-spin Noah Jackpot. Saucers park up to two balls for 2X/3X Noah and release on collect. Middle A+B lights center web for 10s: Add-a-Ball with 10s save below four balls, otherwise 1M. No final objective; ends when multiball ends. Needs machine playtest and presentation polish.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
